--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484587_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484587_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>J. MONTILLA GONZALEZ</t>
+          <t>S. ARNAIZ VEGA</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,67 +565,67 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.8939</v>
+        <v>2.9874</v>
       </c>
       <c r="E2" t="n">
-        <v>3.5174</v>
+        <v>4.0991</v>
       </c>
       <c r="F2" t="n">
-        <v>0.3765</v>
+        <v>-1.1116</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.2256</v>
+        <v>1.6575</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.6484</v>
+        <v>-0.07049999999999999</v>
       </c>
       <c r="I2" t="n">
-        <v>0.4228</v>
+        <v>1.728</v>
       </c>
       <c r="J2" t="n">
-        <v>1.4173</v>
+        <v>2.3736</v>
       </c>
       <c r="K2" t="n">
-        <v>1.2506</v>
+        <v>0.421</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1667</v>
+        <v>1.9526</v>
       </c>
       <c r="M2" t="n">
-        <v>-1.6428</v>
+        <v>-0.7161</v>
       </c>
       <c r="N2" t="n">
-        <v>-1.899</v>
+        <v>-0.4916</v>
       </c>
       <c r="O2" t="n">
-        <v>0.2561</v>
+        <v>-0.2246</v>
       </c>
       <c r="P2" t="n">
-        <v>-2.3823</v>
+        <v>0.1833</v>
       </c>
       <c r="Q2" t="n">
-        <v>-3.6651</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>1.2828</v>
+        <v>0.1833</v>
       </c>
       <c r="S2" t="n">
-        <v>4.5909</v>
+        <v>0.5132</v>
       </c>
       <c r="T2" t="n">
-        <v>3.5325</v>
+        <v>0.1365</v>
       </c>
       <c r="U2" t="n">
-        <v>1.0585</v>
+        <v>0.3767</v>
       </c>
       <c r="V2" t="n">
-        <v>1.9109</v>
+        <v>0.6335</v>
       </c>
       <c r="W2" t="n">
-        <v>2.2328</v>
+        <v>1.5889</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.3219</v>
+        <v>-0.9554</v>
       </c>
     </row>
     <row r="3">
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.375</v>
+        <v>2.3779</v>
       </c>
       <c r="E3" t="n">
-        <v>1.7438</v>
+        <v>1.6477</v>
       </c>
       <c r="F3" t="n">
-        <v>0.6312</v>
+        <v>0.7302999999999999</v>
       </c>
       <c r="G3" t="n">
         <v>-3.1119</v>
@@ -688,13 +688,13 @@
         <v>0.733</v>
       </c>
       <c r="S3" t="n">
-        <v>1.5864</v>
+        <v>1.5894</v>
       </c>
       <c r="T3" t="n">
-        <v>0.5294</v>
+        <v>0.4333</v>
       </c>
       <c r="U3" t="n">
-        <v>1.057</v>
+        <v>1.1561</v>
       </c>
       <c r="V3" t="n">
         <v>3.1674</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>S. ARNAIZ VEGA</t>
+          <t>J. MONTILLA GONZALEZ</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.1628</v>
+        <v>1.5337</v>
       </c>
       <c r="E4" t="n">
-        <v>3.5221</v>
+        <v>1.3059</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.3594</v>
+        <v>0.2279</v>
       </c>
       <c r="G4" t="n">
-        <v>1.6575</v>
+        <v>-0.2256</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.07049999999999999</v>
+        <v>-0.6484</v>
       </c>
       <c r="I4" t="n">
-        <v>1.728</v>
+        <v>0.4228</v>
       </c>
       <c r="J4" t="n">
-        <v>2.3736</v>
+        <v>1.4173</v>
       </c>
       <c r="K4" t="n">
-        <v>0.421</v>
+        <v>1.2506</v>
       </c>
       <c r="L4" t="n">
-        <v>1.9526</v>
+        <v>0.1667</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.7161</v>
+        <v>-1.6428</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.4916</v>
+        <v>-1.899</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.2246</v>
+        <v>0.2561</v>
       </c>
       <c r="P4" t="n">
-        <v>0.1833</v>
+        <v>-2.3823</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>-3.6651</v>
       </c>
       <c r="R4" t="n">
-        <v>0.1833</v>
+        <v>1.2828</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.3115</v>
+        <v>2.2308</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.4404</v>
+        <v>1.3209</v>
       </c>
       <c r="U4" t="n">
-        <v>0.129</v>
+        <v>0.9098000000000001</v>
       </c>
       <c r="V4" t="n">
-        <v>0.6335</v>
+        <v>1.9109</v>
       </c>
       <c r="W4" t="n">
-        <v>1.5889</v>
+        <v>2.2328</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.9554</v>
+        <v>-0.3219</v>
       </c>
     </row>
     <row r="5">
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.2578</v>
+        <v>0.6206</v>
       </c>
       <c r="E5" t="n">
-        <v>0.3862</v>
+        <v>0.6747</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.1284</v>
+        <v>-0.0541</v>
       </c>
       <c r="G5" t="n">
         <v>-0.0663</v>
@@ -844,13 +844,13 @@
         <v>0.3665</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.0425</v>
+        <v>0.3203</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.3673</v>
+        <v>-0.0788</v>
       </c>
       <c r="U5" t="n">
-        <v>0.3248</v>
+        <v>0.3991</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>D. GONZALEZ FERRER</t>
+          <t>J. ARNAIZ VEGA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.101</v>
+        <v>-0.08599999999999999</v>
       </c>
       <c r="E6" t="n">
-        <v>0.5458</v>
+        <v>2.2887</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.4448</v>
+        <v>-2.3747</v>
       </c>
       <c r="G6" t="n">
-        <v>-1.2182</v>
+        <v>2.5588</v>
       </c>
       <c r="H6" t="n">
-        <v>-1.1091</v>
+        <v>0.6866</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.1091</v>
+        <v>1.8722</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.406</v>
+        <v>4.1511</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.4893</v>
+        <v>2.1826</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0833</v>
+        <v>1.9685</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.8122</v>
+        <v>-1.5923</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.6198</v>
+        <v>-1.4959</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.1925</v>
+        <v>-0.0964</v>
       </c>
       <c r="P6" t="n">
-        <v>0.1833</v>
+        <v>-2.9321</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-3.6651</v>
       </c>
       <c r="R6" t="n">
-        <v>0.1833</v>
+        <v>0.733</v>
       </c>
       <c r="S6" t="n">
-        <v>0.5128</v>
+        <v>0.9208</v>
       </c>
       <c r="T6" t="n">
-        <v>0.9517</v>
+        <v>0.2138</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.4389</v>
+        <v>0.707</v>
       </c>
       <c r="V6" t="n">
-        <v>0.6231</v>
+        <v>-0.6335</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.5889</v>
       </c>
       <c r="X6" t="n">
-        <v>0.6231</v>
+        <v>-2.2224</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>J. ARNAIZ VEGA</t>
+          <t>D. GONZALEZ FERRER</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.7213000000000001</v>
+        <v>-0.6132</v>
       </c>
       <c r="E7" t="n">
-        <v>2.0002</v>
+        <v>-0.1684</v>
       </c>
       <c r="F7" t="n">
-        <v>-2.7215</v>
+        <v>-0.4448</v>
       </c>
       <c r="G7" t="n">
-        <v>2.5588</v>
+        <v>-1.2182</v>
       </c>
       <c r="H7" t="n">
-        <v>0.6866</v>
+        <v>-1.1091</v>
       </c>
       <c r="I7" t="n">
-        <v>1.8722</v>
+        <v>-0.1091</v>
       </c>
       <c r="J7" t="n">
-        <v>4.1511</v>
+        <v>-0.406</v>
       </c>
       <c r="K7" t="n">
-        <v>2.1826</v>
+        <v>-0.4893</v>
       </c>
       <c r="L7" t="n">
-        <v>1.9685</v>
+        <v>0.0833</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.5923</v>
+        <v>-0.8122</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.4959</v>
+        <v>-0.6198</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.0964</v>
+        <v>-0.1925</v>
       </c>
       <c r="P7" t="n">
-        <v>-2.9321</v>
+        <v>0.1833</v>
       </c>
       <c r="Q7" t="n">
-        <v>-3.6651</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>0.733</v>
+        <v>0.1833</v>
       </c>
       <c r="S7" t="n">
-        <v>0.2855</v>
+        <v>-0.2014</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.0746</v>
+        <v>0.2376</v>
       </c>
       <c r="U7" t="n">
-        <v>0.3602</v>
+        <v>-0.4389</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.6335</v>
+        <v>0.6231</v>
       </c>
       <c r="W7" t="n">
-        <v>1.5889</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-2.2224</v>
+        <v>0.6231</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.9808</v>
+        <v>-0.6893</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.6869</v>
+        <v>-1.4946</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7062</v>
+        <v>0.8053</v>
       </c>
       <c r="G8" t="n">
         <v>-0.3319</v>
@@ -1078,13 +1078,13 @@
         <v>0.733</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.4656</v>
+        <v>-0.1742</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.3122</v>
+        <v>-0.1199</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.1534</v>
+        <v>-0.0543</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.0979</v>
+        <v>-0.8971</v>
       </c>
       <c r="E9" t="n">
-        <v>2.2647</v>
+        <v>2.4159</v>
       </c>
       <c r="F9" t="n">
-        <v>-3.3626</v>
+        <v>-3.3131</v>
       </c>
       <c r="G9" t="n">
         <v>0.4558</v>
@@ -1156,13 +1156,13 @@
         <v>0.3665</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.3704</v>
+        <v>-0.1697</v>
       </c>
       <c r="T9" t="n">
-        <v>0.2187</v>
+        <v>0.3699</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.5891</v>
+        <v>-0.5396</v>
       </c>
       <c r="V9" t="n">
         <v>-0.6335</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.5046</v>
+        <v>-1.7924</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.5058</v>
+        <v>-0.06610000000000001</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.9988</v>
+        <v>-1.7263</v>
       </c>
       <c r="G10" t="n">
         <v>-1.8666</v>
@@ -1234,13 +1234,13 @@
         <v>0.9163</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.6509</v>
+        <v>-0.9387</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.6425</v>
+        <v>-0.2029</v>
       </c>
       <c r="U10" t="n">
-        <v>-1.0084</v>
+        <v>-0.7359</v>
       </c>
       <c r="V10" t="n">
         <v>2.8455</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.6272</v>
+        <v>-2.2152</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.4234</v>
+        <v>-0.8875999999999999</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.2037</v>
+        <v>-1.3276</v>
       </c>
       <c r="G11" t="n">
         <v>-2.1872</v>
@@ -1312,13 +1312,13 @@
         <v>0.733</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.1625</v>
+        <v>-0.7506</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.5324</v>
+        <v>0.0034</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.6301</v>
+        <v>-0.754</v>
       </c>
       <c r="V11" t="n">
         <v>-0.0104</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.7617</v>
+        <v>-2.7239</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.7096</v>
+        <v>-1.325</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.0521</v>
+        <v>-1.3989</v>
       </c>
       <c r="G12" t="n">
         <v>-1.7938</v>
@@ -1390,13 +1390,13 @@
         <v>0.3665</v>
       </c>
       <c r="S12" t="n">
-        <v>1.4927</v>
+        <v>1.5305</v>
       </c>
       <c r="T12" t="n">
-        <v>0.2187</v>
+        <v>0.6032999999999999</v>
       </c>
       <c r="U12" t="n">
-        <v>1.274</v>
+        <v>0.9272</v>
       </c>
       <c r="V12" t="n">
         <v>-1.9109</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-4.719</v>
+        <v>-4.8491</v>
       </c>
       <c r="E13" t="n">
-        <v>-3.3524</v>
+        <v>-2.9127</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.3666</v>
+        <v>-1.9364</v>
       </c>
       <c r="G13" t="n">
         <v>-2.9831</v>
@@ -1468,13 +1468,13 @@
         <v>0.733</v>
       </c>
       <c r="S13" t="n">
-        <v>0.0258</v>
+        <v>-0.1043</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.5324</v>
+        <v>-0.0927</v>
       </c>
       <c r="U13" t="n">
-        <v>0.5583</v>
+        <v>-0.0115</v>
       </c>
       <c r="V13" t="n">
         <v>-1.5785</v>
@@ -1501,10 +1501,10 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-6.622</v>
+        <v>-6.3466</v>
       </c>
       <c r="E14" t="n">
-        <v>5.302099999999998</v>
+        <v>5.577600000000001</v>
       </c>
       <c r="F14" t="n">
         <v>-11.924</v>
@@ -1546,13 +1546,13 @@
         <v>7.3302</v>
       </c>
       <c r="S14" t="n">
-        <v>4.4907</v>
+        <v>4.7661</v>
       </c>
       <c r="T14" t="n">
-        <v>2.549200000000001</v>
+        <v>2.8244</v>
       </c>
       <c r="U14" t="n">
-        <v>1.9419</v>
+        <v>1.9417</v>
       </c>
       <c r="V14" t="n">
         <v>4.4136</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>6.611</v>
+        <v>7.4166</v>
       </c>
       <c r="E15" t="n">
-        <v>4.5885</v>
+        <v>5.2615</v>
       </c>
       <c r="F15" t="n">
-        <v>2.0225</v>
+        <v>2.1551</v>
       </c>
       <c r="G15" t="n">
         <v>5.085</v>
@@ -1624,13 +1624,13 @@
         <v>2.0158</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.7123</v>
+        <v>-0.9067</v>
       </c>
       <c r="T15" t="n">
-        <v>-1.138</v>
+        <v>-0.4649</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.5743</v>
+        <v>-0.4418</v>
       </c>
       <c r="V15" t="n">
         <v>1.5889</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>4.1547</v>
+        <v>3.7496</v>
       </c>
       <c r="E16" t="n">
-        <v>4.7534</v>
+        <v>4.3687</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.5987</v>
+        <v>-0.6191</v>
       </c>
       <c r="G16" t="n">
         <v>5.2009</v>
@@ -1702,13 +1702,13 @@
         <v>1.4661</v>
       </c>
       <c r="S16" t="n">
-        <v>0.1762</v>
+        <v>-0.2289</v>
       </c>
       <c r="T16" t="n">
-        <v>0.5845</v>
+        <v>0.1999</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.4083</v>
+        <v>-0.4288</v>
       </c>
       <c r="V16" t="n">
         <v>-1.5889</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>3.4044</v>
+        <v>3.7424</v>
       </c>
       <c r="E17" t="n">
-        <v>3.5216</v>
+        <v>3.8101</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.1172</v>
+        <v>-0.0677</v>
       </c>
       <c r="G17" t="n">
         <v>1.8563</v>
@@ -1780,13 +1780,13 @@
         <v>0.9163</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.3523</v>
+        <v>-0.0143</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.5324</v>
+        <v>-0.244</v>
       </c>
       <c r="U17" t="n">
-        <v>0.1801</v>
+        <v>0.2296</v>
       </c>
       <c r="V17" t="n">
         <v>1.9005</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>2.2533</v>
+        <v>3.3781</v>
       </c>
       <c r="E18" t="n">
-        <v>1.2829</v>
+        <v>2.0522</v>
       </c>
       <c r="F18" t="n">
-        <v>0.9704</v>
+        <v>1.3259</v>
       </c>
       <c r="G18" t="n">
         <v>3.857</v>
@@ -1858,13 +1858,13 @@
         <v>2.1991</v>
       </c>
       <c r="S18" t="n">
-        <v>-2.041</v>
+        <v>-0.9163</v>
       </c>
       <c r="T18" t="n">
-        <v>-1.0648</v>
+        <v>-0.2956</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.9762</v>
+        <v>-0.6207</v>
       </c>
       <c r="V18" t="n">
         <v>-1.5785</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>2.1942</v>
+        <v>1.5066</v>
       </c>
       <c r="E19" t="n">
-        <v>2.2294</v>
+        <v>1.3641</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.0352</v>
+        <v>0.1425</v>
       </c>
       <c r="G19" t="n">
         <v>1.5307</v>
@@ -1936,13 +1936,13 @@
         <v>1.4661</v>
       </c>
       <c r="S19" t="n">
-        <v>0.9305</v>
+        <v>0.2428</v>
       </c>
       <c r="T19" t="n">
-        <v>1.2255</v>
+        <v>0.3601</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.295</v>
+        <v>-0.1173</v>
       </c>
       <c r="V19" t="n">
         <v>-0.6335</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>H. BAEZA CABRERA</t>
+          <t>A. MELGAR GARCIA</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,58 +2125,58 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>0.5907</v>
+        <v>0.2977</v>
       </c>
       <c r="E22" t="n">
-        <v>0.7851</v>
+        <v>0</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.1944</v>
+        <v>0.2977</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.586</v>
+        <v>0.2564</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.6788999999999999</v>
+        <v>0.1282</v>
       </c>
       <c r="I22" t="n">
-        <v>0.0929</v>
+        <v>0.1282</v>
       </c>
       <c r="J22" t="n">
-        <v>0.9329</v>
+        <v>0</v>
       </c>
       <c r="K22" t="n">
-        <v>0.8079</v>
+        <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>0.125</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.5189</v>
+        <v>0.2564</v>
       </c>
       <c r="N22" t="n">
-        <v>-1.4867</v>
+        <v>0.1282</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.0321</v>
+        <v>0.1282</v>
       </c>
       <c r="P22" t="n">
-        <v>0.3665</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>-0.1833</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>0.5498</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>0.8101</v>
+        <v>0.0413</v>
       </c>
       <c r="T22" t="n">
-        <v>0.0355</v>
+        <v>0</v>
       </c>
       <c r="U22" t="n">
-        <v>0.7746</v>
+        <v>0.0413</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2191,7 +2191,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A. MELGAR GARCIA</t>
+          <t>H. BAEZA CABRERA</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,58 +2203,58 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>0.2729</v>
+        <v>0.0049</v>
       </c>
       <c r="E23" t="n">
-        <v>0</v>
+        <v>0.4966</v>
       </c>
       <c r="F23" t="n">
-        <v>0.2729</v>
+        <v>-0.4917</v>
       </c>
       <c r="G23" t="n">
-        <v>0.2564</v>
+        <v>-0.586</v>
       </c>
       <c r="H23" t="n">
-        <v>0.1282</v>
+        <v>-0.6788999999999999</v>
       </c>
       <c r="I23" t="n">
-        <v>0.1282</v>
+        <v>0.0929</v>
       </c>
       <c r="J23" t="n">
-        <v>0</v>
+        <v>0.9329</v>
       </c>
       <c r="K23" t="n">
-        <v>0</v>
+        <v>0.8079</v>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>0.125</v>
       </c>
       <c r="M23" t="n">
-        <v>0.2564</v>
+        <v>-1.5189</v>
       </c>
       <c r="N23" t="n">
-        <v>0.1282</v>
+        <v>-1.4867</v>
       </c>
       <c r="O23" t="n">
-        <v>0.1282</v>
+        <v>-0.0321</v>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>0.3665</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>-0.1833</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>0.5498</v>
       </c>
       <c r="S23" t="n">
-        <v>0.0165</v>
+        <v>0.2244</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>-0.253</v>
       </c>
       <c r="U23" t="n">
-        <v>0.0165</v>
+        <v>0.4774</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-2.3995</v>
+        <v>-2.5014</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.6683</v>
+        <v>-1.2452</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.7312</v>
+        <v>-1.2561</v>
       </c>
       <c r="G24" t="n">
         <v>-1.7364</v>
@@ -2326,13 +2326,13 @@
         <v>1.0995</v>
       </c>
       <c r="S24" t="n">
-        <v>0.0095</v>
+        <v>-0.0924</v>
       </c>
       <c r="T24" t="n">
-        <v>0.3643</v>
+        <v>-0.2126</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.3548</v>
+        <v>0.1203</v>
       </c>
       <c r="V24" t="n">
         <v>-1.5889</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-3.9559</v>
+        <v>-3.9209</v>
       </c>
       <c r="E25" t="n">
-        <v>-1.4158</v>
+        <v>-1.6081</v>
       </c>
       <c r="F25" t="n">
-        <v>-2.5401</v>
+        <v>-2.3128</v>
       </c>
       <c r="G25" t="n">
         <v>-3.9216</v>
@@ -2404,13 +2404,13 @@
         <v>0.9163</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.7778</v>
+        <v>-0.7428</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.2767</v>
+        <v>-0.4691</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.5011</v>
+        <v>-0.2738</v>
       </c>
       <c r="V25" t="n">
         <v>0.0104</v>
@@ -2425,7 +2425,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>D. BORISOV</t>
+          <t>D. HOYAS PEREZ</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2437,73 +2437,73 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-4.3556</v>
+        <v>-3.9354</v>
       </c>
       <c r="E26" t="n">
-        <v>-3.0804</v>
+        <v>-2.2352</v>
       </c>
       <c r="F26" t="n">
-        <v>-1.2751</v>
+        <v>-1.7002</v>
       </c>
       <c r="G26" t="n">
-        <v>-4.1822</v>
+        <v>-0.4734</v>
       </c>
       <c r="H26" t="n">
-        <v>0.0037</v>
+        <v>-2.3551</v>
       </c>
       <c r="I26" t="n">
-        <v>-4.1859</v>
+        <v>1.8817</v>
       </c>
       <c r="J26" t="n">
-        <v>-4.3482</v>
+        <v>0.67</v>
       </c>
       <c r="K26" t="n">
-        <v>-0.5793</v>
+        <v>-0.731</v>
       </c>
       <c r="L26" t="n">
-        <v>-3.7689</v>
+        <v>1.401</v>
       </c>
       <c r="M26" t="n">
-        <v>0.1659</v>
+        <v>-1.1434</v>
       </c>
       <c r="N26" t="n">
-        <v>0.583</v>
+        <v>-1.6241</v>
       </c>
       <c r="O26" t="n">
-        <v>-0.417</v>
+        <v>0.4807</v>
       </c>
       <c r="P26" t="n">
-        <v>0.9163</v>
+        <v>-0.9163</v>
       </c>
       <c r="Q26" t="n">
-        <v>-1.0995</v>
+        <v>-2.0158</v>
       </c>
       <c r="R26" t="n">
-        <v>2.0158</v>
+        <v>1.0995</v>
       </c>
       <c r="S26" t="n">
-        <v>-0.7675999999999999</v>
+        <v>-0.3441</v>
       </c>
       <c r="T26" t="n">
-        <v>-0.1666</v>
+        <v>-0.5881999999999999</v>
       </c>
       <c r="U26" t="n">
-        <v>-0.601</v>
+        <v>0.2441</v>
       </c>
       <c r="V26" t="n">
-        <v>-0.3219</v>
+        <v>-2.2016</v>
       </c>
       <c r="W26" t="n">
-        <v>2.5339</v>
+        <v>-0.3011</v>
       </c>
       <c r="X26" t="n">
-        <v>-2.8559</v>
+        <v>-1.9005</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>D. HOYAS PEREZ</t>
+          <t>D. BORISOV</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2515,67 +2515,67 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>-4.3739</v>
+        <v>-4.0598</v>
       </c>
       <c r="E27" t="n">
-        <v>-2.6198</v>
+        <v>-2.8881</v>
       </c>
       <c r="F27" t="n">
-        <v>-1.7541</v>
+        <v>-1.1717</v>
       </c>
       <c r="G27" t="n">
-        <v>-0.4734</v>
+        <v>-4.1822</v>
       </c>
       <c r="H27" t="n">
-        <v>-2.3551</v>
+        <v>0.0037</v>
       </c>
       <c r="I27" t="n">
-        <v>1.8817</v>
+        <v>-4.1859</v>
       </c>
       <c r="J27" t="n">
-        <v>0.67</v>
+        <v>-4.3482</v>
       </c>
       <c r="K27" t="n">
-        <v>-0.731</v>
+        <v>-0.5793</v>
       </c>
       <c r="L27" t="n">
-        <v>1.401</v>
+        <v>-3.7689</v>
       </c>
       <c r="M27" t="n">
-        <v>-1.1434</v>
+        <v>0.1659</v>
       </c>
       <c r="N27" t="n">
-        <v>-1.6241</v>
+        <v>0.583</v>
       </c>
       <c r="O27" t="n">
-        <v>0.4807</v>
+        <v>-0.417</v>
       </c>
       <c r="P27" t="n">
-        <v>-0.9163</v>
+        <v>0.9163</v>
       </c>
       <c r="Q27" t="n">
-        <v>-2.0158</v>
+        <v>-1.0995</v>
       </c>
       <c r="R27" t="n">
-        <v>1.0995</v>
+        <v>2.0158</v>
       </c>
       <c r="S27" t="n">
-        <v>-0.7826</v>
+        <v>-0.4719</v>
       </c>
       <c r="T27" t="n">
-        <v>-0.9728</v>
+        <v>0.0257</v>
       </c>
       <c r="U27" t="n">
-        <v>0.1903</v>
+        <v>-0.4976</v>
       </c>
       <c r="V27" t="n">
-        <v>-2.2016</v>
+        <v>-0.3219</v>
       </c>
       <c r="W27" t="n">
-        <v>-0.3011</v>
+        <v>2.5339</v>
       </c>
       <c r="X27" t="n">
-        <v>-1.9005</v>
+        <v>-2.8559</v>
       </c>
     </row>
     <row r="28">
@@ -2593,16 +2593,16 @@
         <v>1</v>
       </c>
       <c r="D28" t="n">
-        <v>6.621800000000003</v>
+        <v>7.903899999999997</v>
       </c>
       <c r="E28" t="n">
         <v>11.6021</v>
       </c>
       <c r="F28" t="n">
-        <v>-4.9802</v>
+        <v>-3.6981</v>
       </c>
       <c r="G28" t="n">
-        <v>9.1122</v>
+        <v>9.112200000000003</v>
       </c>
       <c r="H28" t="n">
         <v>9.112399999999999</v>
@@ -2617,40 +2617,40 @@
         <v>12.5936</v>
       </c>
       <c r="L28" t="n">
-        <v>-0.3183</v>
+        <v>-0.3183000000000002</v>
       </c>
       <c r="M28" t="n">
-        <v>-3.1628</v>
+        <v>-3.162799999999999</v>
       </c>
       <c r="N28" t="n">
         <v>-3.481</v>
       </c>
       <c r="O28" t="n">
-        <v>0.3184999999999999</v>
+        <v>0.3185000000000001</v>
       </c>
       <c r="P28" t="n">
-        <v>6.413899999999999</v>
+        <v>6.4139</v>
       </c>
       <c r="Q28" t="n">
-        <v>-7.330299999999999</v>
+        <v>-7.3303</v>
       </c>
       <c r="R28" t="n">
         <v>13.7443</v>
       </c>
       <c r="S28" t="n">
-        <v>-4.4908</v>
+        <v>-3.2089</v>
       </c>
       <c r="T28" t="n">
-        <v>-1.941499999999999</v>
+        <v>-1.9417</v>
       </c>
       <c r="U28" t="n">
-        <v>-2.5492</v>
+        <v>-1.2673</v>
       </c>
       <c r="V28" t="n">
         <v>-4.4135</v>
       </c>
       <c r="W28" t="n">
-        <v>8.598899999999999</v>
+        <v>8.5989</v>
       </c>
       <c r="X28" t="n">
         <v>-13.0126</v>
